--- a/V2 BETA/Coparison table High_Temp_3D_Printers_80-100C.xlsx
+++ b/V2 BETA/Coparison table High_Temp_3D_Printers_80-100C.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{20FA6ADF-D3D4-4230-983B-F47C10ED865F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B46385C0-D84F-4CB5-A140-CA308641D84E}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{20FA6ADF-D3D4-4230-983B-F47C10ED865F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A061F412-C6FD-453E-95CA-C3F23A763680}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
     <t>Valkyrie V2 HT100</t>
   </si>
   <si>
-    <t>&lt;120</t>
+    <t>&lt;=120</t>
   </si>
   <si>
     <t>330 x 320 x 290</t>
@@ -629,9 +629,9 @@
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="65.85546875" customWidth="1"/>
-    <col min="7" max="7" width="81.85546875" customWidth="1"/>
-    <col min="8" max="8" width="58" customWidth="1"/>
+    <col min="6" max="6" width="65.85546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="81.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="58" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -685,7 +685,9 @@
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="9"/>
+      <c r="I2" s="9">
+        <v>2500</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
